--- a/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_3.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_3.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
   <si>
     <t xml:space="preserve">YEAR</t>
   </si>
@@ -227,6 +227,63 @@
   </si>
   <si>
     <t>TK_DAY</t>
+  </si>
+  <si>
+    <t>TAIL_NUMBER</t>
+  </si>
+  <si>
+    <t>INIT_AIRPORT</t>
+  </si>
+  <si>
+    <t>INIT_FLYING_TIME</t>
+  </si>
+  <si>
+    <t>INIT_TAKEOFF</t>
+  </si>
+  <si>
+    <t>INIT_FLYING_DAY</t>
+  </si>
+  <si>
+    <t>N121</t>
+  </si>
+  <si>
+    <t>MLX</t>
+  </si>
+  <si>
+    <t>N122</t>
+  </si>
+  <si>
+    <t>ECN</t>
+  </si>
+  <si>
+    <t>N123</t>
+  </si>
+  <si>
+    <t>SAW</t>
+  </si>
+  <si>
+    <t>N124</t>
+  </si>
+  <si>
+    <t>N125</t>
+  </si>
+  <si>
+    <t>N126</t>
+  </si>
+  <si>
+    <t>ESB</t>
+  </si>
+  <si>
+    <t>N127</t>
+  </si>
+  <si>
+    <t>YEI</t>
+  </si>
+  <si>
+    <t>N128</t>
+  </si>
+  <si>
+    <t>HTY</t>
   </si>
 </sst>
 </file>
@@ -511,7 +568,7 @@
   <dimension ref="A1:H355"/>
   <sheetFormatPr defaultColWidth="10.62109375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="1" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A1" t="s" s="1">
         <v>0</v>
       </c>
@@ -537,7 +594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="2" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A2" t="n" s="1">
         <v>2011</v>
       </c>
@@ -563,7 +620,7 @@
         <v>31980</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="3" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A3" t="n" s="1">
         <v>2011</v>
       </c>
@@ -589,7 +646,7 @@
         <v>31990</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="4" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A4" t="n" s="1">
         <v>2011</v>
       </c>
@@ -615,7 +672,7 @@
         <v>31980</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="5" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A5" t="n" s="1">
         <v>2011</v>
       </c>
@@ -641,7 +698,7 @@
         <v>31995</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="6" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A6" t="n" s="1">
         <v>2011</v>
       </c>
@@ -667,7 +724,7 @@
         <v>31995</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="7" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A7" t="n" s="1">
         <v>2011</v>
       </c>
@@ -693,7 +750,7 @@
         <v>32040</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="8" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A8" t="n" s="1">
         <v>2011</v>
       </c>
@@ -719,7 +776,7 @@
         <v>32075</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="9" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A9" t="n" s="1">
         <v>2011</v>
       </c>
@@ -745,7 +802,7 @@
         <v>32100</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="10" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A10" t="n" s="1">
         <v>2011</v>
       </c>
@@ -771,7 +828,7 @@
         <v>32120</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="11" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A11" t="n" s="1">
         <v>2011</v>
       </c>
@@ -797,7 +854,7 @@
         <v>32145</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="12" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A12" t="n" s="1">
         <v>2011</v>
       </c>
@@ -823,7 +880,7 @@
         <v>32155</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="13" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A13" t="n" s="1">
         <v>2011</v>
       </c>
@@ -849,7 +906,7 @@
         <v>32220</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="14" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A14" t="n" s="1">
         <v>2011</v>
       </c>
@@ -875,7 +932,7 @@
         <v>32245</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="15" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A15" t="n" s="1">
         <v>2011</v>
       </c>
@@ -901,7 +958,7 @@
         <v>32235</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="16" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A16" t="n" s="1">
         <v>2011</v>
       </c>
@@ -927,7 +984,7 @@
         <v>32220</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="17" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A17" t="n" s="1">
         <v>2011</v>
       </c>
@@ -953,7 +1010,7 @@
         <v>32285</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="18" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A18" t="n" s="1">
         <v>2011</v>
       </c>
@@ -979,7 +1036,7 @@
         <v>32285</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="19" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A19" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1005,7 +1062,7 @@
         <v>32360</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="20" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A20" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1031,7 +1088,7 @@
         <v>32385</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="21" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A21" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1057,7 +1114,7 @@
         <v>32340</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="22" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A22" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1083,7 +1140,7 @@
         <v>32425</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="23" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A23" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1109,7 +1166,7 @@
         <v>32410</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="24" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A24" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1135,7 +1192,7 @@
         <v>32450</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="25" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A25" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1161,7 +1218,7 @@
         <v>32450</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="26" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A26" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1187,7 +1244,7 @@
         <v>32450</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="27" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A27" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1213,7 +1270,7 @@
         <v>32460</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="28" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A28" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1239,7 +1296,7 @@
         <v>32555</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="29" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A29" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1265,7 +1322,7 @@
         <v>32565</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="30" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A30" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1291,7 +1348,7 @@
         <v>32565</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="31" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A31" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1317,7 +1374,7 @@
         <v>32570</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="32" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A32" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1343,7 +1400,7 @@
         <v>32555</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="33" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A33" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1369,7 +1426,7 @@
         <v>32580</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="34" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A34" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1395,7 +1452,7 @@
         <v>32585</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="35" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A35" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1421,7 +1478,7 @@
         <v>32680</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="36" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A36" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1447,7 +1504,7 @@
         <v>32670</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="37" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A37" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1473,7 +1530,7 @@
         <v>32695</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="38" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A38" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1499,7 +1556,7 @@
         <v>32690</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="39" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A39" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1525,7 +1582,7 @@
         <v>32700</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="40" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A40" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1551,7 +1608,7 @@
         <v>32740</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="41" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A41" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1577,7 +1634,7 @@
         <v>32720</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="42" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A42" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1603,7 +1660,7 @@
         <v>32740</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="43" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A43" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1629,7 +1686,7 @@
         <v>32765</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="44" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A44" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1655,7 +1712,7 @@
         <v>32810</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="45" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A45" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1681,7 +1738,7 @@
         <v>32805</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="46" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A46" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1707,7 +1764,7 @@
         <v>32805</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="47" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A47" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1733,7 +1790,7 @@
         <v>32815</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="48" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A48" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1759,7 +1816,7 @@
         <v>32845</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="49" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A49" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1785,7 +1842,7 @@
         <v>32865</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="50" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A50" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1811,7 +1868,7 @@
         <v>32935</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="51" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A51" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1837,7 +1894,7 @@
         <v>32935</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="52" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A52" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1863,7 +1920,7 @@
         <v>32950</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="53" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A53" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1889,7 +1946,7 @@
         <v>32935</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="54" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A54" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1915,7 +1972,7 @@
         <v>33420</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="55" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A55" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1941,7 +1998,7 @@
         <v>33430</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="56" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A56" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1967,7 +2024,7 @@
         <v>33420</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="57" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A57" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1993,7 +2050,7 @@
         <v>33435</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="58" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A58" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2019,7 +2076,7 @@
         <v>33435</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="59" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A59" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2045,7 +2102,7 @@
         <v>33480</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="60" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A60" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2071,7 +2128,7 @@
         <v>33515</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="61" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A61" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2097,7 +2154,7 @@
         <v>33540</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="62" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A62" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2123,7 +2180,7 @@
         <v>33560</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="63" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A63" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2149,7 +2206,7 @@
         <v>33585</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="64" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A64" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2175,7 +2232,7 @@
         <v>33595</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="65" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A65" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2201,7 +2258,7 @@
         <v>33660</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="66" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A66" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2227,7 +2284,7 @@
         <v>33685</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="67" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A67" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2253,7 +2310,7 @@
         <v>33675</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="68" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A68" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2279,7 +2336,7 @@
         <v>33660</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="69" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A69" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2305,7 +2362,7 @@
         <v>33725</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="70" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A70" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2331,7 +2388,7 @@
         <v>33725</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="71" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A71" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2357,7 +2414,7 @@
         <v>33800</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="72" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A72" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2383,7 +2440,7 @@
         <v>33825</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="73" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A73" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2409,7 +2466,7 @@
         <v>33780</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="74" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A74" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2435,7 +2492,7 @@
         <v>33865</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="75" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A75" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2461,7 +2518,7 @@
         <v>33890</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="76" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A76" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2487,7 +2544,7 @@
         <v>33890</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="77" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A77" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2513,7 +2570,7 @@
         <v>33890</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="78" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A78" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2539,7 +2596,7 @@
         <v>33900</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="79" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A79" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2565,7 +2622,7 @@
         <v>33995</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="80" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A80" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2591,7 +2648,7 @@
         <v>34005</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="81" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A81" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2617,7 +2674,7 @@
         <v>34005</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="82" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A82" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2643,7 +2700,7 @@
         <v>34010</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="83" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A83" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2669,7 +2726,7 @@
         <v>33995</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="84" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A84" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2695,7 +2752,7 @@
         <v>34020</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="85" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A85" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2721,7 +2778,7 @@
         <v>34120</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="86" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A86" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2747,7 +2804,7 @@
         <v>34110</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="87" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A87" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2773,7 +2830,7 @@
         <v>34135</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="88" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A88" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2799,7 +2856,7 @@
         <v>34140</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="89" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A89" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2825,7 +2882,7 @@
         <v>34180</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="90" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A90" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2851,7 +2908,7 @@
         <v>34160</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="91" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A91" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2877,7 +2934,7 @@
         <v>34205</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="92" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A92" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2903,7 +2960,7 @@
         <v>34250</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="93" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A93" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2929,7 +2986,7 @@
         <v>34245</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="94" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A94" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2955,7 +3012,7 @@
         <v>34255</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="95" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A95" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2981,7 +3038,7 @@
         <v>34305</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="96" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A96" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3007,7 +3064,7 @@
         <v>34375</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="97" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A97" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3033,7 +3090,7 @@
         <v>34375</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="98" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A98" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3059,7 +3116,7 @@
         <v>34390</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="99" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A99" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3085,7 +3142,7 @@
         <v>34375</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="100" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A100" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3111,7 +3168,7 @@
         <v>34860</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="101" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A101" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3137,7 +3194,7 @@
         <v>34870</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="102" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A102" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3163,7 +3220,7 @@
         <v>34860</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="103" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A103" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3189,7 +3246,7 @@
         <v>34875</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="104" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A104" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3215,7 +3272,7 @@
         <v>34875</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="105" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A105" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3241,7 +3298,7 @@
         <v>34920</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="106" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A106" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3267,7 +3324,7 @@
         <v>34955</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="107" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A107" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3293,7 +3350,7 @@
         <v>34980</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="108" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A108" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3319,7 +3376,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="109" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A109" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3345,7 +3402,7 @@
         <v>35025</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="110" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A110" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3371,7 +3428,7 @@
         <v>35035</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="111" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A111" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3397,7 +3454,7 @@
         <v>35100</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="112" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A112" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3423,7 +3480,7 @@
         <v>35125</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="113" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A113" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3449,7 +3506,7 @@
         <v>35170</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="114" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A114" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3475,7 +3532,7 @@
         <v>35115</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="115" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A115" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3501,7 +3558,7 @@
         <v>35100</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="116" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A116" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3527,7 +3584,7 @@
         <v>35165</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="117" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A117" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3553,7 +3610,7 @@
         <v>35165</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="118" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A118" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3579,7 +3636,7 @@
         <v>35165</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="119" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A119" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3605,7 +3662,7 @@
         <v>35240</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="120" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A120" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3631,7 +3688,7 @@
         <v>35220</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="121" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A121" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3657,7 +3714,7 @@
         <v>35265</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="122" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A122" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3683,7 +3740,7 @@
         <v>35265</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="123" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A123" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3709,7 +3766,7 @@
         <v>35305</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="124" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A124" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3735,7 +3792,7 @@
         <v>35290</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="125" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A125" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3761,7 +3818,7 @@
         <v>35390</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="126" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A126" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3787,7 +3844,7 @@
         <v>35330</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="127" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A127" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3813,7 +3870,7 @@
         <v>35330</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="128" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A128" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3839,7 +3896,7 @@
         <v>35340</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="129" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A129" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3865,7 +3922,7 @@
         <v>35435</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="130" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A130" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3891,7 +3948,7 @@
         <v>35445</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="131" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A131" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3917,7 +3974,7 @@
         <v>35450</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="132" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A132" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3943,7 +4000,7 @@
         <v>35435</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="133" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A133" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3969,7 +4026,7 @@
         <v>35460</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="134" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A134" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3995,7 +4052,7 @@
         <v>35465</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="135" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A135" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4021,7 +4078,7 @@
         <v>35560</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="136" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A136" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4047,7 +4104,7 @@
         <v>35550</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="137" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A137" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4073,7 +4130,7 @@
         <v>35575</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="138" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A138" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4099,7 +4156,7 @@
         <v>35570</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="139" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A139" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4125,7 +4182,7 @@
         <v>35580</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="140" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A140" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4151,7 +4208,7 @@
         <v>35620</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="141" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A141" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4177,7 +4234,7 @@
         <v>35600</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="142" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A142" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4203,7 +4260,7 @@
         <v>35620</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="143" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A143" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4229,7 +4286,7 @@
         <v>35645</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="144" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A144" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4255,7 +4312,7 @@
         <v>35690</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="145" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A145" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4281,7 +4338,7 @@
         <v>35685</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="146" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A146" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4307,7 +4364,7 @@
         <v>35685</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="147" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A147" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4333,7 +4390,7 @@
         <v>35695</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="148" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A148" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4359,7 +4416,7 @@
         <v>35745</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="149" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A149" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4385,7 +4442,7 @@
         <v>35725</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="150" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A150" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4411,7 +4468,7 @@
         <v>35815</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="151" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A151" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4437,7 +4494,7 @@
         <v>35815</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="152" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A152" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4463,7 +4520,7 @@
         <v>35830</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="153" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A153" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4489,7 +4546,7 @@
         <v>35815</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="154" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A154" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4515,7 +4572,7 @@
         <v>36300</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="155" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A155" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4541,7 +4598,7 @@
         <v>36310</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="156" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A156" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4567,7 +4624,7 @@
         <v>36300</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="157" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A157" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4593,7 +4650,7 @@
         <v>36315</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="158" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A158" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4619,7 +4676,7 @@
         <v>36315</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="159" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A159" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4645,7 +4702,7 @@
         <v>36360</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="160" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A160" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4671,7 +4728,7 @@
         <v>36395</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="161" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A161" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4697,7 +4754,7 @@
         <v>36420</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="162" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A162" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4723,7 +4780,7 @@
         <v>36440</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="163" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A163" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4749,7 +4806,7 @@
         <v>36465</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="164" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A164" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4775,7 +4832,7 @@
         <v>36475</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="165" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A165" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4801,7 +4858,7 @@
         <v>36540</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="166" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A166" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4827,7 +4884,7 @@
         <v>36565</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="167" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A167" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4853,7 +4910,7 @@
         <v>36555</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="168" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A168" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4879,7 +4936,7 @@
         <v>36540</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="169" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A169" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4905,7 +4962,7 @@
         <v>36605</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="170" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A170" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4931,7 +4988,7 @@
         <v>36605</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="171" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A171" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4957,7 +5014,7 @@
         <v>36680</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="172" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A172" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4983,7 +5040,7 @@
         <v>36660</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="173" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A173" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5009,7 +5066,7 @@
         <v>36705</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="174" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A174" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5035,7 +5092,7 @@
         <v>36745</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="175" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A175" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5061,7 +5118,7 @@
         <v>36730</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="176" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A176" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5087,7 +5144,7 @@
         <v>36770</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="177" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A177" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5113,7 +5170,7 @@
         <v>36770</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="178" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A178" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5139,7 +5196,7 @@
         <v>36770</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="179" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A179" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5165,7 +5222,7 @@
         <v>36780</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="180" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A180" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5191,7 +5248,7 @@
         <v>36875</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="181" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A181" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5217,7 +5274,7 @@
         <v>36885</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="182" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A182" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5243,7 +5300,7 @@
         <v>36885</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="183" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A183" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5269,7 +5326,7 @@
         <v>36890</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="184" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A184" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5295,7 +5352,7 @@
         <v>36875</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="185" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A185" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5321,7 +5378,7 @@
         <v>36900</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="186" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A186" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5347,7 +5404,7 @@
         <v>36905</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="187" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A187" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5373,7 +5430,7 @@
         <v>37000</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="188" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A188" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5399,7 +5456,7 @@
         <v>36990</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="189" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A189" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5425,7 +5482,7 @@
         <v>37015</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="190" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A190" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5451,7 +5508,7 @@
         <v>37010</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="191" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A191" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5477,7 +5534,7 @@
         <v>37020</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="192" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A192" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5503,7 +5560,7 @@
         <v>37060</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="193" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A193" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5529,7 +5586,7 @@
         <v>37040</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="194" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A194" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5555,7 +5612,7 @@
         <v>37060</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="195" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A195" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5581,7 +5638,7 @@
         <v>37085</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="196" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A196" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5607,7 +5664,7 @@
         <v>37130</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="197" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A197" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5633,7 +5690,7 @@
         <v>37125</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="198" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A198" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5659,7 +5716,7 @@
         <v>37125</v>
       </c>
     </row>
-    <row r="199" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="199" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A199" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5685,7 +5742,7 @@
         <v>37135</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="200" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A200" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5711,7 +5768,7 @@
         <v>37185</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="201" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A201" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5737,7 +5794,7 @@
         <v>37165</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="202" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A202" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5763,7 +5820,7 @@
         <v>37255</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="203" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A203" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5789,7 +5846,7 @@
         <v>37255</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="204" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A204" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5815,7 +5872,7 @@
         <v>37270</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="205" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A205" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5841,7 +5898,7 @@
         <v>37255</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="206" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A206" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5867,7 +5924,7 @@
         <v>37740</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="207" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A207" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5893,7 +5950,7 @@
         <v>37750</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="208" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A208" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5919,7 +5976,7 @@
         <v>37740</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="209" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A209" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5945,7 +6002,7 @@
         <v>37755</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="210" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A210" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5971,7 +6028,7 @@
         <v>37755</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="211" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A211" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5997,7 +6054,7 @@
         <v>37800</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="212" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A212" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6023,7 +6080,7 @@
         <v>37835</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="213" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A213" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6049,7 +6106,7 @@
         <v>37860</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="214" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A214" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6075,7 +6132,7 @@
         <v>37880</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="215" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A215" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6101,7 +6158,7 @@
         <v>37905</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="216" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A216" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6127,7 +6184,7 @@
         <v>37915</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="217" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A217" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6153,7 +6210,7 @@
         <v>37980</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="218" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A218" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6179,7 +6236,7 @@
         <v>38005</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="219" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A219" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6205,7 +6262,7 @@
         <v>37995</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="220" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A220" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6231,7 +6288,7 @@
         <v>37980</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="221" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A221" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6257,7 +6314,7 @@
         <v>38045</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="222" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A222" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6283,7 +6340,7 @@
         <v>38045</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="223" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A223" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6309,7 +6366,7 @@
         <v>38045</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="224" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A224" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6335,7 +6392,7 @@
         <v>38120</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="225" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A225" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6361,7 +6418,7 @@
         <v>38145</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="226" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A226" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6387,7 +6444,7 @@
         <v>38100</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="227" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A227" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6413,7 +6470,7 @@
         <v>38145</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="228" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A228" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6439,7 +6496,7 @@
         <v>38185</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="229" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A229" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6465,7 +6522,7 @@
         <v>38170</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="230" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A230" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6491,7 +6548,7 @@
         <v>38210</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="231" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A231" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6517,7 +6574,7 @@
         <v>38210</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="232" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A232" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6543,7 +6600,7 @@
         <v>38210</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="233" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A233" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6569,7 +6626,7 @@
         <v>38220</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="234" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A234" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6595,7 +6652,7 @@
         <v>38315</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="235" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A235" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6621,7 +6678,7 @@
         <v>38325</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="236" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A236" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6647,7 +6704,7 @@
         <v>38325</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="237" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A237" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6673,7 +6730,7 @@
         <v>38330</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="238" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A238" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6699,7 +6756,7 @@
         <v>38315</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="239" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A239" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6725,7 +6782,7 @@
         <v>38340</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="240" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A240" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6751,7 +6808,7 @@
         <v>38345</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="241" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A241" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6777,7 +6834,7 @@
         <v>38440</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="242" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A242" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6803,7 +6860,7 @@
         <v>38430</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="243" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A243" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6829,7 +6886,7 @@
         <v>38455</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="244" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A244" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6855,7 +6912,7 @@
         <v>38450</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="245" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A245" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6881,7 +6938,7 @@
         <v>38460</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="246" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A246" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6907,7 +6964,7 @@
         <v>38500</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="247" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A247" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6933,7 +6990,7 @@
         <v>38480</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="248" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A248" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6959,7 +7016,7 @@
         <v>38500</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="249" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A249" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6985,7 +7042,7 @@
         <v>38525</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="250" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A250" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7011,7 +7068,7 @@
         <v>38570</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="251" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A251" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7037,7 +7094,7 @@
         <v>38565</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="252" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A252" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7063,7 +7120,7 @@
         <v>38565</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="253" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A253" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7089,7 +7146,7 @@
         <v>38575</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="254" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A254" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7115,7 +7172,7 @@
         <v>38625</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="255" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A255" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7141,7 +7198,7 @@
         <v>38605</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="256" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A256" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7167,7 +7224,7 @@
         <v>38695</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="257" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A257" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7193,7 +7250,7 @@
         <v>38695</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="258" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A258" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7219,7 +7276,7 @@
         <v>38710</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="259" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A259" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7245,7 +7302,7 @@
         <v>38695</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="260" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A260" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7271,7 +7328,7 @@
         <v>39180</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="261" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A261" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7297,7 +7354,7 @@
         <v>39195</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="262" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A262" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7323,7 +7380,7 @@
         <v>39195</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="263" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A263" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7349,7 +7406,7 @@
         <v>39190</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="264" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A264" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7375,7 +7432,7 @@
         <v>39180</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="265" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A265" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7401,7 +7458,7 @@
         <v>39275</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="266" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A266" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7427,7 +7484,7 @@
         <v>39320</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="267" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A267" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7453,7 +7510,7 @@
         <v>39355</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="268" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A268" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7479,7 +7536,7 @@
         <v>39420</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="269" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A269" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7505,7 +7562,7 @@
         <v>39445</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="270" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A270" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7531,7 +7588,7 @@
         <v>39490</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="271" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A271" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7557,7 +7614,7 @@
         <v>39435</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="272" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A272" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7583,7 +7640,7 @@
         <v>39420</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="273" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A273" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7609,7 +7666,7 @@
         <v>39485</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="274" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A274" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7635,7 +7692,7 @@
         <v>39560</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="275" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A275" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7661,7 +7718,7 @@
         <v>39540</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="276" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A276" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7687,7 +7744,7 @@
         <v>39585</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="277" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A277" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7713,7 +7770,7 @@
         <v>39625</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="278" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A278" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7739,7 +7796,7 @@
         <v>39630</v>
       </c>
     </row>
-    <row r="279" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="279" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A279" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7765,7 +7822,7 @@
         <v>39710</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="280" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A280" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7791,7 +7848,7 @@
         <v>39650</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="281" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A281" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7817,7 +7874,7 @@
         <v>39650</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="282" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A282" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7843,7 +7900,7 @@
         <v>39660</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="283" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A283" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7869,7 +7926,7 @@
         <v>39755</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="284" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A284" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7895,7 +7952,7 @@
         <v>39745</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="285" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A285" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7921,7 +7978,7 @@
         <v>39765</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="286" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A286" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7947,7 +8004,7 @@
         <v>39770</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="287" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A287" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7973,7 +8030,7 @@
         <v>39755</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="288" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A288" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7999,7 +8056,7 @@
         <v>39780</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="289" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A289" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8025,7 +8082,7 @@
         <v>39880</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="290" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A290" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8051,7 +8108,7 @@
         <v>39870</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="291" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A291" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8077,7 +8134,7 @@
         <v>39895</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="292" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A292" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8103,7 +8160,7 @@
         <v>39900</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="293" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A293" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8129,7 +8186,7 @@
         <v>39940</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="294" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A294" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8155,7 +8212,7 @@
         <v>39920</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="295" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A295" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8181,7 +8238,7 @@
         <v>39965</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="296" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A296" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8207,7 +8264,7 @@
         <v>40010</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="297" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A297" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8233,7 +8290,7 @@
         <v>40005</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="298" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A298" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8259,7 +8316,7 @@
         <v>40015</v>
       </c>
     </row>
-    <row r="299" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="299" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A299" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8285,7 +8342,7 @@
         <v>40065</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="300" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A300" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8311,7 +8368,7 @@
         <v>40135</v>
       </c>
     </row>
-    <row r="301" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="301" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A301" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8337,7 +8394,7 @@
         <v>40135</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="302" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A302" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8363,7 +8420,7 @@
         <v>40150</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="303" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A303" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8389,7 +8446,7 @@
         <v>40135</v>
       </c>
     </row>
-    <row r="304" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="304" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A304" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8415,7 +8472,7 @@
         <v>40620</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="305" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A305" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8441,7 +8498,7 @@
         <v>40630</v>
       </c>
     </row>
-    <row r="306" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="306" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A306" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8467,7 +8524,7 @@
         <v>40620</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="307" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A307" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8493,7 +8550,7 @@
         <v>40635</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="308" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A308" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8519,7 +8576,7 @@
         <v>40635</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="309" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A309" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8545,7 +8602,7 @@
         <v>40715</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="310" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A310" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8571,7 +8628,7 @@
         <v>40760</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="311" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A311" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8597,7 +8654,7 @@
         <v>40785</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="312" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A312" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8623,7 +8680,7 @@
         <v>40795</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="313" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A313" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8649,7 +8706,7 @@
         <v>40860</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="314" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A314" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8675,7 +8732,7 @@
         <v>40885</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="315" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A315" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8701,7 +8758,7 @@
         <v>40875</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="316" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A316" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8727,7 +8784,7 @@
         <v>40860</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="317" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A317" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8753,7 +8810,7 @@
         <v>40925</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="318" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A318" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8779,7 +8836,7 @@
         <v>40925</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="319" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A319" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8805,7 +8862,7 @@
         <v>40925</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="320" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A320" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8831,7 +8888,7 @@
         <v>41000</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="321" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A321" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8857,7 +8914,7 @@
         <v>40980</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="322" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A322" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8883,7 +8940,7 @@
         <v>41025</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="323" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A323" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8909,7 +8966,7 @@
         <v>41025</v>
       </c>
     </row>
-    <row r="324" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="324" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A324" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8935,7 +8992,7 @@
         <v>41065</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="325" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A325" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8961,7 +9018,7 @@
         <v>41050</v>
       </c>
     </row>
-    <row r="326" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="326" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A326" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8987,7 +9044,7 @@
         <v>41090</v>
       </c>
     </row>
-    <row r="327" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="327" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A327" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9013,7 +9070,7 @@
         <v>41090</v>
       </c>
     </row>
-    <row r="328" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="328" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A328" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9039,7 +9096,7 @@
         <v>41090</v>
       </c>
     </row>
-    <row r="329" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="329" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A329" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9065,7 +9122,7 @@
         <v>41100</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="330" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A330" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9091,7 +9148,7 @@
         <v>41195</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="331" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A331" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9117,7 +9174,7 @@
         <v>41205</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="332" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A332" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9143,7 +9200,7 @@
         <v>41205</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="333" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A333" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9169,7 +9226,7 @@
         <v>41210</v>
       </c>
     </row>
-    <row r="334" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="334" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A334" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9195,7 +9252,7 @@
         <v>41195</v>
       </c>
     </row>
-    <row r="335" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="335" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A335" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9221,7 +9278,7 @@
         <v>41220</v>
       </c>
     </row>
-    <row r="336" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="336" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A336" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9247,7 +9304,7 @@
         <v>41225</v>
       </c>
     </row>
-    <row r="337" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="337" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A337" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9273,7 +9330,7 @@
         <v>41320</v>
       </c>
     </row>
-    <row r="338" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="338" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A338" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9299,7 +9356,7 @@
         <v>41310</v>
       </c>
     </row>
-    <row r="339" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="339" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A339" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9325,7 +9382,7 @@
         <v>41335</v>
       </c>
     </row>
-    <row r="340" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="340" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A340" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9351,7 +9408,7 @@
         <v>41330</v>
       </c>
     </row>
-    <row r="341" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="341" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A341" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9377,7 +9434,7 @@
         <v>41340</v>
       </c>
     </row>
-    <row r="342" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="342" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A342" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9403,7 +9460,7 @@
         <v>41380</v>
       </c>
     </row>
-    <row r="343" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="343" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A343" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9429,7 +9486,7 @@
         <v>41360</v>
       </c>
     </row>
-    <row r="344" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="344" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A344" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9455,7 +9512,7 @@
         <v>41380</v>
       </c>
     </row>
-    <row r="345" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="345" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A345" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9481,7 +9538,7 @@
         <v>41405</v>
       </c>
     </row>
-    <row r="346" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="346" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A346" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9507,7 +9564,7 @@
         <v>41450</v>
       </c>
     </row>
-    <row r="347" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="347" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A347" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9533,7 +9590,7 @@
         <v>41445</v>
       </c>
     </row>
-    <row r="348" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="348" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A348" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9559,7 +9616,7 @@
         <v>41445</v>
       </c>
     </row>
-    <row r="349" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="349" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A349" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9585,7 +9642,7 @@
         <v>41455</v>
       </c>
     </row>
-    <row r="350" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="350" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A350" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9611,7 +9668,7 @@
         <v>41505</v>
       </c>
     </row>
-    <row r="351" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="351" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A351" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9637,7 +9694,7 @@
         <v>41485</v>
       </c>
     </row>
-    <row r="352" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="352" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A352" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9663,7 +9720,7 @@
         <v>41575</v>
       </c>
     </row>
-    <row r="353" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="353" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A353" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9689,7 +9746,7 @@
         <v>41575</v>
       </c>
     </row>
-    <row r="354" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="354" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A354" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9715,7 +9772,7 @@
         <v>41590</v>
       </c>
     </row>
-    <row r="355" spans="1:8" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="355" spans="1:8" hidden="false" outlineLevel="0" ht="15.75" customHeight="false" collapsed="false" customFormat="false">
       <c r="A355" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9760,7 +9817,7 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:10" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="1" spans="1:10" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -9792,7 +9849,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="2" spans="1:10" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A2">
         <v>35</v>
       </c>
@@ -9843,7 +9900,7 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="1" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A1" t="s" s="1">
         <v>36</v>
       </c>
@@ -9869,7 +9926,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="2" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A2" t="s" s="1">
         <v>24</v>
       </c>
@@ -9895,7 +9952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="3" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A3" t="s" s="1">
         <v>9</v>
       </c>
@@ -9921,7 +9978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="4" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A4" t="s" s="1">
         <v>16</v>
       </c>
@@ -9947,7 +10004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="5" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A5" t="s" s="1">
         <v>25</v>
       </c>
@@ -9973,7 +10030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="6" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A6" t="s" s="1">
         <v>22</v>
       </c>
@@ -9999,7 +10056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="7" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A7" t="s" s="1">
         <v>17</v>
       </c>
@@ -10025,7 +10082,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="8" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A8" t="s" s="1">
         <v>10</v>
       </c>
@@ -10051,7 +10108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="9" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A9" t="s" s="1">
         <v>20</v>
       </c>
@@ -10077,7 +10134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="10" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A10" t="s" s="1">
         <v>11</v>
       </c>
@@ -10103,7 +10160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="11" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A11" t="s" s="1">
         <v>29</v>
       </c>
@@ -10129,7 +10186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="12" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A12" t="s" s="1">
         <v>23</v>
       </c>
@@ -10155,7 +10212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="13" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A13" t="s" s="1">
         <v>14</v>
       </c>
@@ -10181,7 +10238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="14" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A14" t="s" s="1">
         <v>27</v>
       </c>
@@ -10207,7 +10264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="15" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A15" t="s" s="1">
         <v>13</v>
       </c>
@@ -10233,7 +10290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="16" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A16" t="s" s="1">
         <v>44</v>
       </c>
@@ -10259,7 +10316,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="17" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A17" t="s" s="1">
         <v>28</v>
       </c>
@@ -10285,7 +10342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="18" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A18" t="s" s="1">
         <v>8</v>
       </c>
@@ -10311,7 +10368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="19" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A19" t="s" s="1">
         <v>26</v>
       </c>
@@ -10337,7 +10394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="20" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A20" t="s" s="1">
         <v>15</v>
       </c>
@@ -10363,7 +10420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="21" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A21" t="s" s="1">
         <v>18</v>
       </c>
@@ -10389,7 +10446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="22" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A22" t="s" s="1">
         <v>21</v>
       </c>
@@ -10415,7 +10472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="false" customFormat="false" ht="12.8" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="23" spans="1:8" hidden="false" outlineLevel="0" ht="12.8" customHeight="false" collapsed="false" customFormat="false">
       <c r="A23" t="s" s="0">
         <v>12</v>
       </c>
@@ -10460,157 +10517,156 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A1" t="s" s="1">
-        <v>45</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>46</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>47</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>48</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A2" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="B2" t="s" s="3">
-        <v>13</v>
-      </c>
-      <c r="C2" t="n" s="3">
-        <f>6000-935</f>
+    <row r="1" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2">
         <v>5065</v>
       </c>
-      <c r="D2" t="n" s="1">
+      <c r="D2">
         <v>42</v>
       </c>
-      <c r="E2" t="n" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A3" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s" s="3">
-        <v>10</v>
-      </c>
-      <c r="C3" t="n" s="3">
+      <c r="E2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="n" s="1">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="E3" t="n" s="1">
+    </row>
+    <row r="4" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A4" t="s" s="1">
-        <v>52</v>
-      </c>
-      <c r="B4" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="C4" t="n" s="3">
+    <row r="5" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5">
         <v>0</v>
       </c>
-      <c r="D4" t="n" s="1">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="E4" t="n" s="1">
+    </row>
+    <row r="6" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A5" t="s" s="1">
-        <v>53</v>
-      </c>
-      <c r="B5" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="C5" t="n" s="3">
+    <row r="7" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7">
         <v>0</v>
       </c>
-      <c r="D5" t="n" s="1">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="E5" t="n" s="1">
+    </row>
+    <row r="8" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A6" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="B6" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="C6" t="n" s="3">
+    <row r="9" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9">
         <v>0</v>
       </c>
-      <c r="D6" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A7" t="s" s="1">
-        <v>55</v>
-      </c>
-      <c r="B7" t="s" s="3">
-        <v>11</v>
-      </c>
-      <c r="C7" t="n" s="3">
+      <c r="D9">
         <v>0</v>
       </c>
-      <c r="D7" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A8" t="s" s="1">
-        <v>56</v>
-      </c>
-      <c r="B8" t="s" s="3">
-        <v>12</v>
-      </c>
-      <c r="C8" t="n" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A9" t="s" s="1">
-        <v>57</v>
-      </c>
-      <c r="B9" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="C9" t="n" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n" s="1">
+      <c r="E9">
         <v>1</v>
       </c>
     </row>

--- a/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_3.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_3.xlsx
@@ -9848,10 +9848,10 @@
         <v>480</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>78.0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12.0</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -9928,7 +9928,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -9988,25 +9988,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -10014,7 +10014,7 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -10073,10 +10073,10 @@
         <v>5065</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>66.0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
